--- a/Feuilles/Vibrations.xlsx
+++ b/Feuilles/Vibrations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141180EE-06AE-1B41-BB52-0C8B5B3E8931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBC75FA-C31A-5B44-844E-C90B400FC243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="2240" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>MES</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>END</t>
+  </si>
+  <si>
+    <t>LOOP</t>
   </si>
 </sst>
 </file>
@@ -449,10 +452,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -465,8 +468,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -480,7 +486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -491,7 +497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -502,7 +508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -513,7 +519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -527,7 +533,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -538,7 +544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -549,7 +555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -560,7 +566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -571,7 +577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -582,7 +588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -593,7 +599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -604,7 +610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -615,7 +621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -626,7 +632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>

--- a/Feuilles/Vibrations.xlsx
+++ b/Feuilles/Vibrations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBC75FA-C31A-5B44-844E-C90B400FC243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1919CD62-B1E4-EC44-AE88-5ADB86C2E83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="2240" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -833,7 +833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -847,7 +847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -913,7 +913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -935,7 +935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -957,7 +957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -968,7 +968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1003,8 +1003,11 @@
       <c r="D48" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1015,7 +1018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1026,7 +1029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1037,7 +1040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1048,7 +1051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1059,7 +1062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1070,7 +1073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1081,7 +1084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1092,7 +1095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1103,7 +1106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1114,7 +1117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1125,7 +1128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1136,7 +1139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1147,7 +1150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1160,8 +1163,11 @@
       <c r="D62" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1172,7 +1178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1183,7 +1189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1194,7 +1200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1205,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1216,7 +1222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1227,7 +1233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1238,7 +1244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1249,7 +1255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1262,8 +1268,11 @@
       <c r="D71" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1274,7 +1283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1285,7 +1294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1296,7 +1305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1307,7 +1316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1318,7 +1327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1329,7 +1338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1340,7 +1349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1351,7 +1360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1362,7 +1371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1373,7 +1382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1384,7 +1393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1395,7 +1404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1406,7 +1415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1419,8 +1428,11 @@
       <c r="D85" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1431,7 +1443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1442,7 +1454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1453,7 +1465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1464,7 +1476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1475,7 +1487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1486,7 +1498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1497,7 +1509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1508,7 +1520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1519,7 +1531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1530,7 +1542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -1541,7 +1553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -1552,7 +1564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -1563,7 +1575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -1576,8 +1588,11 @@
       <c r="D99" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -1588,7 +1603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -1599,7 +1614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -1610,7 +1625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -1621,7 +1636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -1632,7 +1647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -1643,7 +1658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -1654,7 +1669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -1665,7 +1680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -1676,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -1687,7 +1702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -1698,7 +1713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -1709,7 +1724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
